--- a/testData/loginData.xlsx
+++ b/testData/loginData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Test\Selenium\SeleniumTestAutomationFramework\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E23F3810-FC44-4179-A3D1-4F3BCA2BA497}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24056B7F-3ADE-4BDC-9BD3-75461C8AA5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>emailAddress</t>
   </si>
@@ -34,6 +34,9 @@
   </si>
   <si>
     <t>dummy6thmay@test.com</t>
+  </si>
+  <si>
+    <t>12345</t>
   </si>
 </sst>
 </file>
@@ -78,9 +81,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -364,10 +368,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="36.21875" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -381,13 +381,13 @@
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2">
-        <v>12345</v>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" xr:uid="{833346A2-C452-4E26-A8EB-A64F85D5AC89}"/>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{72417457-A030-44F3-9D8E-4D5F785246FC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
